--- a/plate3d/PLATE3D_CRANE.xlsx
+++ b/plate3d/PLATE3D_CRANE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="114">
   <si>
     <t>tower crane - PLATE3D demo</t>
   </si>
@@ -238,6 +238,9 @@
     <t>XZ</t>
   </si>
   <si>
+    <t>BASE</t>
+  </si>
+  <si>
     <t>ONE jib bay: triangular, 2000 long</t>
   </si>
   <si>
@@ -251,9 +254,6 @@
   </si>
   <si>
     <t>md.base</t>
-  </si>
-  <si>
-    <t>BASE</t>
   </si>
   <si>
     <t>operator cab</t>
@@ -746,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N124"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1457,10 +1457,10 @@
         <v>6</v>
       </c>
       <c r="F30">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="F31">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G31">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1515,10 +1515,10 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G32">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -1544,10 +1544,10 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="F34">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>2000</v>
@@ -1602,10 +1602,10 @@
         <v>6</v>
       </c>
       <c r="F35">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H35">
         <v>2000</v>
@@ -1631,10 +1631,10 @@
         <v>6</v>
       </c>
       <c r="F36">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H36">
         <v>2000</v>
@@ -1660,10 +1660,10 @@
         <v>6</v>
       </c>
       <c r="F37">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H37">
         <v>2000</v>
@@ -1689,10 +1689,10 @@
         <v>6</v>
       </c>
       <c r="F38">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>6</v>
       </c>
       <c r="F39">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G39">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -1759,10 +1759,10 @@
         <v>6</v>
       </c>
       <c r="F40">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -1794,10 +1794,10 @@
         <v>6</v>
       </c>
       <c r="F41">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G41">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -1829,10 +1829,10 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -1864,10 +1864,10 @@
         <v>6</v>
       </c>
       <c r="F43">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -1899,10 +1899,10 @@
         <v>6</v>
       </c>
       <c r="F44">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G44">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -1934,10 +1934,10 @@
         <v>6</v>
       </c>
       <c r="F45">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="G45">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -1952,79 +1952,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>2</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>61</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E48" t="s">
         <v>62</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F48" t="s">
         <v>63</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G48" t="s">
         <v>64</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H48" t="s">
         <v>65</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I48" t="s">
         <v>66</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J48" t="s">
         <v>67</v>
       </c>
-      <c r="K47" t="s">
+      <c r="K48" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <v>-600</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-      <c r="I48" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
@@ -2036,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2053,7 +2044,7 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
@@ -2065,10 +2056,10 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H50">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I50" t="s">
         <v>73</v>
@@ -2082,10 +2073,10 @@
         <v>70</v>
       </c>
       <c r="C51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E51" t="s">
         <v>6</v>
@@ -2097,45 +2088,39 @@
         <v>600</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="I51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" t="s">
+        <v>77</v>
+      </c>
+      <c r="D52" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" t="s">
+        <v>6</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>1200</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" t="s">
-        <v>76</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>600</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52" t="s">
-        <v>72</v>
-      </c>
-      <c r="J52">
-        <v>26.565</v>
-      </c>
-      <c r="K52">
-        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2146,7 +2131,7 @@
         <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2158,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>-600</v>
+        <v>1200</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2167,7 +2152,7 @@
         <v>72</v>
       </c>
       <c r="J53">
-        <v>-26.565</v>
+        <v>26.565</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -2181,10 +2166,10 @@
         <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
         <v>6</v>
@@ -2193,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -2202,144 +2187,132 @@
         <v>72</v>
       </c>
       <c r="J54">
+        <v>-26.565</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55" t="s">
+        <v>72</v>
+      </c>
+      <c r="J55">
         <v>-30.964</v>
       </c>
-      <c r="K54">
+      <c r="K55">
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" t="s">
+        <v>77</v>
+      </c>
+      <c r="D56" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C58" t="s">
         <v>2</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D58" t="s">
         <v>61</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E58" t="s">
         <v>62</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F58" t="s">
         <v>63</v>
       </c>
-      <c r="G56" t="s">
+      <c r="G58" t="s">
         <v>64</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H58" t="s">
         <v>65</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I58" t="s">
         <v>66</v>
       </c>
-      <c r="J56" t="s">
+      <c r="J58" t="s">
         <v>67</v>
       </c>
-      <c r="K56" t="s">
+      <c r="K58" t="s">
         <v>68</v>
       </c>
-      <c r="L56" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
+      <c r="L58" t="s">
         <v>78</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D57" t="s">
+      <c r="B59" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" t="s">
         <v>32</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E59" t="s">
         <v>35</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" t="s">
-        <v>36</v>
-      </c>
-      <c r="E58" t="s">
-        <v>38</v>
-      </c>
-      <c r="F58">
-        <v>600</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
-      <c r="H58">
-        <v>20</v>
-      </c>
-      <c r="I58" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" t="s">
-        <v>36</v>
-      </c>
-      <c r="E59" t="s">
-        <v>38</v>
-      </c>
-      <c r="F59">
-        <v>-600</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59">
-        <v>20</v>
-      </c>
-      <c r="I59" t="s">
-        <v>74</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>0</v>
-      </c>
-      <c r="L59">
-        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2350,7 +2323,7 @@
         <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D60" t="s">
         <v>36</v>
@@ -2359,16 +2332,16 @@
         <v>38</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G60">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H60">
         <v>20</v>
       </c>
       <c r="I60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2379,7 +2352,7 @@
         <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D61" t="s">
         <v>36</v>
@@ -2388,16 +2361,16 @@
         <v>38</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G61">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -2409,7 +2382,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>6</v>
       </c>
@@ -2417,114 +2390,123 @@
         <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D62" t="s">
+        <v>36</v>
+      </c>
+      <c r="E62" t="s">
+        <v>38</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>600</v>
+      </c>
+      <c r="H62">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" t="s">
         <v>80</v>
       </c>
-      <c r="E62" t="s">
+      <c r="D63" t="s">
+        <v>36</v>
+      </c>
+      <c r="E63" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>-600</v>
+      </c>
+      <c r="H63">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>73</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" t="s">
         <v>32</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F64" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="s">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C66" t="s">
         <v>2</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D66" t="s">
         <v>61</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E66" t="s">
         <v>62</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F66" t="s">
         <v>63</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G66" t="s">
         <v>64</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H66" t="s">
         <v>65</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I66" t="s">
         <v>66</v>
       </c>
-      <c r="J64" t="s">
+      <c r="J66" t="s">
         <v>67</v>
       </c>
-      <c r="K64" t="s">
+      <c r="K66" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" t="s">
-        <v>82</v>
-      </c>
-      <c r="D65" t="s">
-        <v>40</v>
-      </c>
-      <c r="E65" t="s">
-        <v>35</v>
-      </c>
-      <c r="F65">
-        <v>0</v>
-      </c>
-      <c r="G65">
-        <v>-650</v>
-      </c>
-      <c r="H65">
-        <v>800</v>
-      </c>
-      <c r="I65" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" t="s">
-        <v>82</v>
-      </c>
-      <c r="D66" t="s">
-        <v>40</v>
-      </c>
-      <c r="E66" t="s">
-        <v>35</v>
-      </c>
-      <c r="F66">
-        <v>0</v>
-      </c>
-      <c r="G66">
-        <v>650</v>
-      </c>
-      <c r="H66">
-        <v>800</v>
-      </c>
-      <c r="I66" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>70</v>
@@ -2533,22 +2515,22 @@
         <v>82</v>
       </c>
       <c r="D67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E67" t="s">
         <v>35</v>
       </c>
       <c r="F67">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>-650</v>
       </c>
       <c r="H67">
         <v>800</v>
       </c>
       <c r="I67" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2562,7 +2544,7 @@
         <v>82</v>
       </c>
       <c r="D68" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E68" t="s">
         <v>35</v>
@@ -2571,13 +2553,13 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I68" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -2591,25 +2573,25 @@
         <v>82</v>
       </c>
       <c r="D69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E69" t="s">
         <v>35</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>1600</v>
+        <v>800</v>
       </c>
       <c r="I69" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>6</v>
       </c>
@@ -2620,111 +2602,111 @@
         <v>82</v>
       </c>
       <c r="D70" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="E70" t="s">
+        <v>35</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C71" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" t="s">
         <v>42</v>
       </c>
-      <c r="F70" t="s">
+      <c r="E71" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>1600</v>
+      </c>
+      <c r="I71" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" t="s">
+        <v>75</v>
+      </c>
+      <c r="E72" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C74" t="s">
         <v>2</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D74" t="s">
         <v>61</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E74" t="s">
         <v>62</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F74" t="s">
         <v>63</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G74" t="s">
         <v>64</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H74" t="s">
         <v>65</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I74" t="s">
         <v>66</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J74" t="s">
         <v>67</v>
       </c>
-      <c r="K72" t="s">
+      <c r="K74" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" t="s">
-        <v>84</v>
-      </c>
-      <c r="D73" t="s">
-        <v>57</v>
-      </c>
-      <c r="E73" t="s">
-        <v>59</v>
-      </c>
-      <c r="F73">
-        <v>-1500</v>
-      </c>
-      <c r="G73">
-        <v>-700</v>
-      </c>
-      <c r="H73">
-        <v>-320</v>
-      </c>
-      <c r="I73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" t="s">
-        <v>84</v>
-      </c>
-      <c r="D74" t="s">
-        <v>57</v>
-      </c>
-      <c r="E74" t="s">
-        <v>59</v>
-      </c>
-      <c r="F74">
-        <v>-1500</v>
-      </c>
-      <c r="G74">
-        <v>700</v>
-      </c>
-      <c r="H74">
-        <v>-320</v>
-      </c>
-      <c r="I74" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>70</v>
@@ -2733,25 +2715,25 @@
         <v>84</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>-320</v>
       </c>
       <c r="I75" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>6</v>
       </c>
@@ -2762,123 +2744,111 @@
         <v>84</v>
       </c>
       <c r="D76" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="E76" t="s">
+        <v>59</v>
+      </c>
+      <c r="F76">
+        <v>-1500</v>
+      </c>
+      <c r="G76">
+        <v>700</v>
+      </c>
+      <c r="H76">
+        <v>-320</v>
+      </c>
+      <c r="I76" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C77" t="s">
+        <v>84</v>
+      </c>
+      <c r="D77" t="s">
         <v>39</v>
       </c>
-      <c r="F76" t="s">
+      <c r="E77" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>60</v>
+      <c r="B78" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C78" t="s">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="D78" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E78" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="F78" t="s">
-        <v>63</v>
-      </c>
-      <c r="G78" t="s">
-        <v>64</v>
-      </c>
-      <c r="H78" t="s">
-        <v>65</v>
-      </c>
-      <c r="I78" t="s">
-        <v>66</v>
-      </c>
-      <c r="J78" t="s">
-        <v>67</v>
-      </c>
-      <c r="K78" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C79" t="s">
-        <v>86</v>
-      </c>
-      <c r="D79" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79">
-        <v>1500</v>
-      </c>
-      <c r="G79">
-        <v>1500</v>
-      </c>
-      <c r="H79">
-        <v>18200</v>
-      </c>
-      <c r="I79" t="s">
-        <v>72</v>
-      </c>
-      <c r="J79">
-        <v>14.984</v>
-      </c>
-      <c r="K79">
-        <v>-15.524</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>70</v>
+      <c r="B80" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="C80" t="s">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="E80" t="s">
-        <v>6</v>
-      </c>
-      <c r="F80">
-        <v>-1500</v>
-      </c>
-      <c r="G80">
-        <v>1500</v>
-      </c>
-      <c r="H80">
-        <v>18200</v>
+        <v>62</v>
+      </c>
+      <c r="F80" t="s">
+        <v>63</v>
+      </c>
+      <c r="G80" t="s">
+        <v>64</v>
+      </c>
+      <c r="H80" t="s">
+        <v>65</v>
       </c>
       <c r="I80" t="s">
-        <v>72</v>
-      </c>
-      <c r="J80">
-        <v>14.984</v>
-      </c>
-      <c r="K80">
-        <v>15.524</v>
+        <v>66</v>
+      </c>
+      <c r="J80" t="s">
+        <v>67</v>
+      </c>
+      <c r="K80" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>70</v>
@@ -2893,13 +2863,13 @@
         <v>6</v>
       </c>
       <c r="F81">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="I81" t="s">
         <v>72</v>
@@ -2928,13 +2898,13 @@
         <v>6</v>
       </c>
       <c r="F82">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="G82">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="H82">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="I82" t="s">
         <v>72</v>
@@ -2946,7 +2916,7 @@
         <v>-15.524</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>6</v>
       </c>
@@ -2957,25 +2927,31 @@
         <v>86</v>
       </c>
       <c r="D83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E83" t="s">
         <v>6</v>
       </c>
       <c r="F83">
-        <v>-1500</v>
+        <v>3000</v>
       </c>
       <c r="G83">
-        <v>-1500</v>
+        <v>3000</v>
       </c>
       <c r="H83">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="J83">
+        <v>14.984</v>
+      </c>
+      <c r="K83">
+        <v>-15.524</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>6</v>
       </c>
@@ -2986,22 +2962,28 @@
         <v>86</v>
       </c>
       <c r="D84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E84" t="s">
         <v>6</v>
       </c>
       <c r="F84">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="H84">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="J84">
+        <v>14.984</v>
+      </c>
+      <c r="K84">
+        <v>15.524</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -3021,16 +3003,16 @@
         <v>6</v>
       </c>
       <c r="F85">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -3050,143 +3032,134 @@
         <v>6</v>
       </c>
       <c r="F86">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="H86">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="I86" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" t="s">
+        <v>86</v>
+      </c>
+      <c r="D87" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>3000</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C88" t="s">
+        <v>86</v>
+      </c>
+      <c r="D88" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" t="s">
+        <v>6</v>
+      </c>
+      <c r="F88">
+        <v>3000</v>
+      </c>
+      <c r="G88">
+        <v>3000</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C89" t="s">
+        <v>86</v>
+      </c>
+      <c r="D89" t="s">
+        <v>75</v>
+      </c>
+      <c r="E89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C91" t="s">
         <v>2</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D91" t="s">
         <v>61</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E91" t="s">
         <v>62</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F91" t="s">
         <v>63</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G91" t="s">
         <v>64</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H91" t="s">
         <v>65</v>
       </c>
-      <c r="I88" t="s">
+      <c r="I91" t="s">
         <v>66</v>
       </c>
-      <c r="J88" t="s">
+      <c r="J91" t="s">
         <v>67</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K91" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C89" t="s">
-        <v>88</v>
-      </c>
-      <c r="D89" t="s">
-        <v>43</v>
-      </c>
-      <c r="E89" t="s">
-        <v>35</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C90" t="s">
-        <v>88</v>
-      </c>
-      <c r="D90" t="s">
-        <v>43</v>
-      </c>
-      <c r="E90" t="s">
-        <v>35</v>
-      </c>
-      <c r="F90">
-        <v>260</v>
-      </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-      <c r="I90" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C91" t="s">
-        <v>88</v>
-      </c>
-      <c r="D91" t="s">
-        <v>43</v>
-      </c>
-      <c r="E91" t="s">
-        <v>35</v>
-      </c>
-      <c r="F91">
-        <v>520</v>
-      </c>
-      <c r="G91">
-        <v>0</v>
-      </c>
-      <c r="H91">
-        <v>0</v>
-      </c>
-      <c r="I91" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>70</v>
@@ -3195,152 +3168,140 @@
         <v>88</v>
       </c>
       <c r="D92" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="E92" t="s">
+        <v>35</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C93" t="s">
+        <v>88</v>
+      </c>
+      <c r="D93" t="s">
         <v>43</v>
       </c>
-      <c r="F92" t="s">
+      <c r="E93" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="F93">
+        <v>260</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>60</v>
+      <c r="B94" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="C94" t="s">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="D94" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E94" t="s">
-        <v>62</v>
-      </c>
-      <c r="F94" t="s">
-        <v>63</v>
-      </c>
-      <c r="G94" t="s">
-        <v>64</v>
-      </c>
-      <c r="H94" t="s">
-        <v>65</v>
+        <v>35</v>
+      </c>
+      <c r="F94">
+        <v>520</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>66</v>
-      </c>
-      <c r="J94" t="s">
-        <v>67</v>
-      </c>
-      <c r="K94" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D95" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="E95" t="s">
+        <v>43</v>
+      </c>
+      <c r="F95" t="s">
         <v>35</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="G95">
-        <v>0</v>
-      </c>
-      <c r="H95">
-        <v>0</v>
-      </c>
-      <c r="I95" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C96" t="s">
-        <v>90</v>
-      </c>
-      <c r="D96" t="s">
-        <v>21</v>
-      </c>
-      <c r="E96" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
-      </c>
-      <c r="G96">
-        <v>-260</v>
-      </c>
-      <c r="H96">
-        <v>-400</v>
-      </c>
-      <c r="I96" t="s">
-        <v>72</v>
-      </c>
-      <c r="J96">
-        <v>180</v>
-      </c>
-      <c r="K96">
-        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>70</v>
+      <c r="B97" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="C97" t="s">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97">
-        <v>0</v>
-      </c>
-      <c r="G97">
-        <v>260</v>
-      </c>
-      <c r="H97">
-        <v>-400</v>
+        <v>62</v>
+      </c>
+      <c r="F97" t="s">
+        <v>63</v>
+      </c>
+      <c r="G97" t="s">
+        <v>64</v>
+      </c>
+      <c r="H97" t="s">
+        <v>65</v>
       </c>
       <c r="I97" t="s">
-        <v>72</v>
-      </c>
-      <c r="J97">
-        <v>180</v>
-      </c>
-      <c r="K97">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="J97" t="s">
+        <v>67</v>
+      </c>
+      <c r="K97" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>70</v>
@@ -3349,7 +3310,7 @@
         <v>90</v>
       </c>
       <c r="D98" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E98" t="s">
         <v>35</v>
@@ -3361,13 +3322,13 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <v>-13460</v>
+        <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>6</v>
       </c>
@@ -3378,155 +3339,202 @@
         <v>90</v>
       </c>
       <c r="D99" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E99" t="s">
+        <v>6</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>-260</v>
+      </c>
+      <c r="H99">
+        <v>-400</v>
+      </c>
+      <c r="I99" t="s">
+        <v>72</v>
+      </c>
+      <c r="J99">
+        <v>180</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" t="s">
+        <v>90</v>
+      </c>
+      <c r="D100" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" t="s">
+        <v>6</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>260</v>
+      </c>
+      <c r="H100">
+        <v>-400</v>
+      </c>
+      <c r="I100" t="s">
+        <v>72</v>
+      </c>
+      <c r="J100">
+        <v>180</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C101" t="s">
+        <v>90</v>
+      </c>
+      <c r="D101" t="s">
+        <v>45</v>
+      </c>
+      <c r="E101" t="s">
+        <v>35</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>-13460</v>
+      </c>
+      <c r="I101" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" t="s">
+        <v>90</v>
+      </c>
+      <c r="D102" t="s">
+        <v>75</v>
+      </c>
+      <c r="E102" t="s">
         <v>44</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F102" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B101" s="2" t="s">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C104" t="s">
         <v>2</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D104" t="s">
         <v>92</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E104" t="s">
         <v>93</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F104" t="s">
         <v>94</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G104" t="s">
         <v>95</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H104" t="s">
         <v>96</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I104" t="s">
         <v>97</v>
       </c>
-      <c r="J101" t="s">
+      <c r="J104" t="s">
         <v>68</v>
       </c>
-      <c r="K101" t="s">
+      <c r="K104" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C102" t="s">
-        <v>101</v>
-      </c>
-      <c r="D102" t="s">
-        <v>71</v>
-      </c>
-      <c r="E102" t="s">
-        <v>102</v>
-      </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C103" t="s">
-        <v>101</v>
-      </c>
-      <c r="D103" t="s">
-        <v>101</v>
-      </c>
-      <c r="E103" t="s">
-        <v>103</v>
-      </c>
-      <c r="F103">
-        <v>0</v>
-      </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-      <c r="H103">
-        <v>2000</v>
-      </c>
-      <c r="I103">
-        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D105" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E105" t="s">
         <v>102</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="H105">
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B107" s="3" t="s">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C107" t="s">
-        <v>105</v>
-      </c>
-      <c r="D107" t="s">
-        <v>84</v>
-      </c>
-      <c r="E107" t="s">
-        <v>102</v>
-      </c>
-      <c r="F107">
-        <v>0</v>
-      </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-      <c r="H107">
-        <v>18000</v>
+      <c r="C106" t="s">
+        <v>101</v>
+      </c>
+      <c r="D106" t="s">
+        <v>101</v>
+      </c>
+      <c r="E106" t="s">
+        <v>103</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>2000</v>
+      </c>
+      <c r="I106">
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -3537,10 +3545,10 @@
         <v>100</v>
       </c>
       <c r="C108" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D108" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E108" t="s">
         <v>102</v>
@@ -3555,59 +3563,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B109" s="3" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B110" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C110" t="s">
         <v>105</v>
       </c>
-      <c r="D109" t="s">
-        <v>82</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="D110" t="s">
+        <v>84</v>
+      </c>
+      <c r="E110" t="s">
         <v>102</v>
       </c>
-      <c r="F109">
-        <v>1500</v>
-      </c>
-      <c r="G109">
-        <v>0</v>
-      </c>
-      <c r="H109">
-        <v>16100</v>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>18000</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C111" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D111" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E111" t="s">
         <v>102</v>
       </c>
       <c r="F111">
-        <v>1400</v>
+        <v>-1500</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="H111">
-        <v>18400</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>6</v>
       </c>
@@ -3615,61 +3623,49 @@
         <v>100</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D112" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E112" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F112">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G112">
         <v>0</v>
       </c>
       <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C114" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D114" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E114" t="s">
         <v>102</v>
       </c>
       <c r="F114">
-        <v>-1400</v>
+        <v>1400</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="H114">
         <v>18400</v>
       </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>180</v>
-      </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
@@ -3679,16 +3675,16 @@
         <v>100</v>
       </c>
       <c r="C115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D115" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E115" t="s">
         <v>103</v>
       </c>
       <c r="F115">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -3697,71 +3693,74 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D117" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E117" t="s">
         <v>102</v>
       </c>
       <c r="F117">
-        <v>-9000</v>
+        <v>-1400</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H117">
-        <v>18700</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B119" s="3" t="s">
+        <v>18400</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B118" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C119" t="s">
-        <v>111</v>
-      </c>
-      <c r="D119" t="s">
-        <v>18</v>
-      </c>
-      <c r="E119" t="s">
-        <v>102</v>
-      </c>
-      <c r="F119">
-        <v>0</v>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>23600</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>106.621</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C118" t="s">
+        <v>109</v>
+      </c>
+      <c r="D118" t="s">
+        <v>109</v>
+      </c>
+      <c r="E118" t="s">
+        <v>103</v>
+      </c>
+      <c r="F118">
+        <v>-2000</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>6</v>
       </c>
@@ -3769,34 +3768,25 @@
         <v>100</v>
       </c>
       <c r="C120" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D120" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="E120" t="s">
         <v>102</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="G120">
         <v>0</v>
       </c>
       <c r="H120">
-        <v>23600</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>-118.393</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>6</v>
       </c>
@@ -3804,29 +3794,99 @@
         <v>100</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D122" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="E122" t="s">
         <v>102</v>
       </c>
       <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>23600</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>106.621</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C123" t="s">
+        <v>111</v>
+      </c>
+      <c r="D123" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" t="s">
+        <v>102</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>23600</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>-118.393</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C125" t="s">
+        <v>112</v>
+      </c>
+      <c r="D125" t="s">
+        <v>90</v>
+      </c>
+      <c r="E125" t="s">
+        <v>102</v>
+      </c>
+      <c r="F125">
         <v>12000</v>
       </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
         <v>18100</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B124" s="3" t="s">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>113</v>
       </c>
     </row>

--- a/plate3d/PLATE3D_CRANE.xlsx
+++ b/plate3d/PLATE3D_CRANE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="158">
   <si>
     <t>tower crane - PLATE3D demo</t>
   </si>
@@ -229,15 +229,63 @@
     <t>md.mast</t>
   </si>
   <si>
+    <t>bar.leg_1</t>
+  </si>
+  <si>
     <t>XY</t>
   </si>
   <si>
+    <t>bar.leg_2</t>
+  </si>
+  <si>
+    <t>bar.leg_3</t>
+  </si>
+  <si>
+    <t>bar.leg_4</t>
+  </si>
+  <si>
+    <t>bar.tie_1</t>
+  </si>
+  <si>
     <t>YZ</t>
   </si>
   <si>
+    <t>bar.tie_2</t>
+  </si>
+  <si>
+    <t>bar.tie_3</t>
+  </si>
+  <si>
     <t>XZ</t>
   </si>
   <si>
+    <t>bar.tie_4</t>
+  </si>
+  <si>
+    <t>bar.dia_1</t>
+  </si>
+  <si>
+    <t>bar.dia_2</t>
+  </si>
+  <si>
+    <t>bar.dia_3</t>
+  </si>
+  <si>
+    <t>bar.dia_4</t>
+  </si>
+  <si>
+    <t>bar.dia_5</t>
+  </si>
+  <si>
+    <t>bar.dia_6</t>
+  </si>
+  <si>
+    <t>bar.dia_7</t>
+  </si>
+  <si>
+    <t>bar.dia_8</t>
+  </si>
+  <si>
     <t>BASE</t>
   </si>
   <si>
@@ -247,6 +295,21 @@
     <t>md.jib</t>
   </si>
   <si>
+    <t>bar.chord_1</t>
+  </si>
+  <si>
+    <t>bar.chord_2</t>
+  </si>
+  <si>
+    <t>bar.chord_3</t>
+  </si>
+  <si>
+    <t>bar.web_1</t>
+  </si>
+  <si>
+    <t>bar.web_2</t>
+  </si>
+  <si>
     <t>ROT.Z</t>
   </si>
   <si>
@@ -256,34 +319,103 @@
     <t>md.base</t>
   </si>
   <si>
+    <t>pl.gus_1</t>
+  </si>
+  <si>
+    <t>pl.gus_2</t>
+  </si>
+  <si>
+    <t>pl.gus_3</t>
+  </si>
+  <si>
+    <t>pl.gus_4</t>
+  </si>
+  <si>
     <t>operator cab</t>
   </si>
   <si>
     <t>md.cab</t>
   </si>
   <si>
+    <t>pl.cabs_1</t>
+  </si>
+  <si>
+    <t>pl.cabs_2</t>
+  </si>
+  <si>
+    <t>pl.cabt_1</t>
+  </si>
+  <si>
+    <t>pl.cabt_2</t>
+  </si>
+  <si>
     <t>slewing platform</t>
   </si>
   <si>
     <t>md.top</t>
   </si>
   <si>
+    <t>sc.H300_1</t>
+  </si>
+  <si>
+    <t>sc.H300_2</t>
+  </si>
+  <si>
     <t>A-frame over the mast</t>
   </si>
   <si>
     <t>md.afr</t>
   </si>
   <si>
+    <t>bar.aleg_1</t>
+  </si>
+  <si>
+    <t>bar.aleg_2</t>
+  </si>
+  <si>
+    <t>bar.aleg_3</t>
+  </si>
+  <si>
+    <t>bar.aleg_4</t>
+  </si>
+  <si>
+    <t>bar.atie_1</t>
+  </si>
+  <si>
+    <t>bar.atie_2</t>
+  </si>
+  <si>
+    <t>bar.atie_3</t>
+  </si>
+  <si>
+    <t>bar.atie_4</t>
+  </si>
+  <si>
     <t>counterweight, 3 slabs</t>
   </si>
   <si>
     <t>md.cwt</t>
   </si>
   <si>
+    <t>pl.cw_1</t>
+  </si>
+  <si>
+    <t>pl.cw_2</t>
+  </si>
+  <si>
+    <t>pl.cw_3</t>
+  </si>
+  <si>
     <t>trolley, ropes, hook</t>
   </si>
   <si>
     <t>md.hook</t>
+  </si>
+  <si>
+    <t>bar.rope_1</t>
+  </si>
+  <si>
+    <t>bar.rope_2</t>
   </si>
   <si>
     <t># ASSY</t>
@@ -1451,7 +1583,7 @@
         <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E30" t="s">
         <v>6</v>
@@ -1466,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1480,7 +1612,7 @@
         <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -1495,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1509,7 +1641,7 @@
         <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
         <v>6</v>
@@ -1524,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1538,7 +1670,7 @@
         <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
         <v>6</v>
@@ -1553,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1567,7 +1699,7 @@
         <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -1582,7 +1714,7 @@
         <v>2000</v>
       </c>
       <c r="I34" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -1596,7 +1728,7 @@
         <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="E35" t="s">
         <v>6</v>
@@ -1611,7 +1743,7 @@
         <v>2000</v>
       </c>
       <c r="I35" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1625,7 +1757,7 @@
         <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E36" t="s">
         <v>6</v>
@@ -1640,7 +1772,7 @@
         <v>2000</v>
       </c>
       <c r="I36" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -1654,7 +1786,7 @@
         <v>71</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
@@ -1669,7 +1801,7 @@
         <v>2000</v>
       </c>
       <c r="I37" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1683,7 +1815,7 @@
         <v>71</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
         <v>6</v>
@@ -1698,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -1718,7 +1850,7 @@
         <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="E39" t="s">
         <v>6</v>
@@ -1733,7 +1865,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -1753,7 +1885,7 @@
         <v>71</v>
       </c>
       <c r="D40" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="E40" t="s">
         <v>6</v>
@@ -1768,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -1788,7 +1920,7 @@
         <v>71</v>
       </c>
       <c r="D41" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
         <v>6</v>
@@ -1803,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -1823,7 +1955,7 @@
         <v>71</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E42" t="s">
         <v>6</v>
@@ -1838,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J42">
         <v>-30.964</v>
@@ -1858,7 +1990,7 @@
         <v>71</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="E43" t="s">
         <v>6</v>
@@ -1873,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J43">
         <v>30.964</v>
@@ -1893,7 +2025,7 @@
         <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="E44" t="s">
         <v>6</v>
@@ -1908,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J44">
         <v>-30.964</v>
@@ -1928,7 +2060,7 @@
         <v>71</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="E45" t="s">
         <v>6</v>
@@ -1943,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J45">
         <v>30.964</v>
@@ -1963,10 +2095,10 @@
         <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="F46" t="s">
         <v>35</v>
@@ -2009,16 +2141,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C49" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="E49" t="s">
         <v>6</v>
@@ -2033,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2044,10 +2176,10 @@
         <v>70</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
         <v>6</v>
@@ -2062,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2073,10 +2205,10 @@
         <v>70</v>
       </c>
       <c r="C51" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D51" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="E51" t="s">
         <v>6</v>
@@ -2091,7 +2223,7 @@
         <v>1200</v>
       </c>
       <c r="I51" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2102,7 +2234,7 @@
         <v>70</v>
       </c>
       <c r="C52" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
         <v>14</v>
@@ -2120,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2131,10 +2263,10 @@
         <v>70</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="E53" t="s">
         <v>6</v>
@@ -2149,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J53">
         <v>26.565</v>
@@ -2166,10 +2298,10 @@
         <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="E54" t="s">
         <v>6</v>
@@ -2184,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J54">
         <v>-26.565</v>
@@ -2201,7 +2333,7 @@
         <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D55" t="s">
         <v>15</v>
@@ -2219,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J55">
         <v>-30.964</v>
@@ -2236,13 +2368,13 @@
         <v>70</v>
       </c>
       <c r="C56" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F56" t="s">
         <v>35</v>
@@ -2283,18 +2415,18 @@
         <v>68</v>
       </c>
       <c r="L58" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D59" t="s">
         <v>32</v>
@@ -2312,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2323,10 +2455,10 @@
         <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D60" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="E60" t="s">
         <v>38</v>
@@ -2341,7 +2473,7 @@
         <v>20</v>
       </c>
       <c r="I60" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2352,10 +2484,10 @@
         <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D61" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="E61" t="s">
         <v>38</v>
@@ -2370,7 +2502,7 @@
         <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -2390,10 +2522,10 @@
         <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D62" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="E62" t="s">
         <v>38</v>
@@ -2408,7 +2540,7 @@
         <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -2419,10 +2551,10 @@
         <v>70</v>
       </c>
       <c r="C63" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D63" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="E63" t="s">
         <v>38</v>
@@ -2437,7 +2569,7 @@
         <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -2457,10 +2589,10 @@
         <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D64" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E64" t="s">
         <v>32</v>
@@ -2506,16 +2638,16 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D67" t="s">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="E67" t="s">
         <v>35</v>
@@ -2530,7 +2662,7 @@
         <v>800</v>
       </c>
       <c r="I67" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -2541,10 +2673,10 @@
         <v>70</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>40</v>
+        <v>109</v>
       </c>
       <c r="E68" t="s">
         <v>35</v>
@@ -2559,7 +2691,7 @@
         <v>800</v>
       </c>
       <c r="I68" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -2570,7 +2702,7 @@
         <v>70</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D69" t="s">
         <v>41</v>
@@ -2588,7 +2720,7 @@
         <v>800</v>
       </c>
       <c r="I69" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2599,10 +2731,10 @@
         <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="E70" t="s">
         <v>35</v>
@@ -2617,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -2628,10 +2760,10 @@
         <v>70</v>
       </c>
       <c r="C71" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D71" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="E71" t="s">
         <v>35</v>
@@ -2646,7 +2778,7 @@
         <v>1600</v>
       </c>
       <c r="I71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2657,13 +2789,13 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="F72" t="s">
         <v>35</v>
@@ -2706,16 +2838,16 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D75" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="E75" t="s">
         <v>59</v>
@@ -2730,7 +2862,7 @@
         <v>-320</v>
       </c>
       <c r="I75" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -2741,10 +2873,10 @@
         <v>70</v>
       </c>
       <c r="C76" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D76" t="s">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="E76" t="s">
         <v>59</v>
@@ -2759,7 +2891,7 @@
         <v>-320</v>
       </c>
       <c r="I76" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -2770,7 +2902,7 @@
         <v>70</v>
       </c>
       <c r="C77" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
         <v>39</v>
@@ -2788,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2799,10 +2931,10 @@
         <v>70</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="D78" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E78" t="s">
         <v>39</v>
@@ -2848,16 +2980,16 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C81" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="E81" t="s">
         <v>6</v>
@@ -2872,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J81">
         <v>-14.984</v>
@@ -2889,10 +3021,10 @@
         <v>70</v>
       </c>
       <c r="C82" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="E82" t="s">
         <v>6</v>
@@ -2907,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J82">
         <v>-14.984</v>
@@ -2924,10 +3056,10 @@
         <v>70</v>
       </c>
       <c r="C83" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="E83" t="s">
         <v>6</v>
@@ -2942,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J83">
         <v>14.984</v>
@@ -2959,10 +3091,10 @@
         <v>70</v>
       </c>
       <c r="C84" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="E84" t="s">
         <v>6</v>
@@ -2977,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J84">
         <v>14.984</v>
@@ -2994,10 +3126,10 @@
         <v>70</v>
       </c>
       <c r="C85" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D85" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="E85" t="s">
         <v>6</v>
@@ -3012,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -3023,10 +3155,10 @@
         <v>70</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="E86" t="s">
         <v>6</v>
@@ -3041,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -3052,10 +3184,10 @@
         <v>70</v>
       </c>
       <c r="C87" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="E87" t="s">
         <v>6</v>
@@ -3070,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -3081,10 +3213,10 @@
         <v>70</v>
       </c>
       <c r="C88" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="E88" t="s">
         <v>6</v>
@@ -3099,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3110,13 +3242,13 @@
         <v>70</v>
       </c>
       <c r="C89" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="D89" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="F89" t="s">
         <v>35</v>
@@ -3159,16 +3291,16 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="E92" t="s">
         <v>35</v>
@@ -3183,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3194,10 +3326,10 @@
         <v>70</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D93" t="s">
-        <v>43</v>
+        <v>129</v>
       </c>
       <c r="E93" t="s">
         <v>35</v>
@@ -3212,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3223,10 +3355,10 @@
         <v>70</v>
       </c>
       <c r="C94" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D94" t="s">
-        <v>43</v>
+        <v>130</v>
       </c>
       <c r="E94" t="s">
         <v>35</v>
@@ -3241,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3252,13 +3384,13 @@
         <v>70</v>
       </c>
       <c r="C95" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="D95" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E95" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="F95" t="s">
         <v>35</v>
@@ -3301,13 +3433,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C98" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D98" t="s">
         <v>44</v>
@@ -3325,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -3336,10 +3468,10 @@
         <v>70</v>
       </c>
       <c r="C99" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D99" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="E99" t="s">
         <v>6</v>
@@ -3354,7 +3486,7 @@
         <v>-400</v>
       </c>
       <c r="I99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J99">
         <v>180</v>
@@ -3371,10 +3503,10 @@
         <v>70</v>
       </c>
       <c r="C100" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D100" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="E100" t="s">
         <v>6</v>
@@ -3389,7 +3521,7 @@
         <v>-400</v>
       </c>
       <c r="I100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J100">
         <v>180</v>
@@ -3406,7 +3538,7 @@
         <v>70</v>
       </c>
       <c r="C101" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D101" t="s">
         <v>45</v>
@@ -3424,7 +3556,7 @@
         <v>-13460</v>
       </c>
       <c r="I101" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3435,10 +3567,10 @@
         <v>70</v>
       </c>
       <c r="C102" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D102" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E102" t="s">
         <v>44</v>
@@ -3452,51 +3584,51 @@
         <v>6</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="C104" t="s">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="E104" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="F104" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="G104" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="H104" t="s">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="I104" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="J104" t="s">
         <v>68</v>
       </c>
       <c r="K104" t="s">
-        <v>98</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C105" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="D105" t="s">
         <v>71</v>
       </c>
       <c r="E105" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F105">
         <v>-600</v>
@@ -3513,16 +3645,16 @@
         <v>6</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C106" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="D106" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
       <c r="E106" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -3542,16 +3674,16 @@
         <v>6</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C108" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="D108" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E108" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -3568,16 +3700,16 @@
         <v>6</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C110" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D110" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="E110" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -3594,16 +3726,16 @@
         <v>6</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C111" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D111" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="E111" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F111">
         <v>-1500</v>
@@ -3620,16 +3752,16 @@
         <v>6</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C112" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="D112" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E112" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F112">
         <v>1500</v>
@@ -3643,19 +3775,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C114" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E114" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F114">
         <v>1400</v>
@@ -3672,16 +3804,16 @@
         <v>6</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C115" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D115" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="E115" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F115">
         <v>2000</v>
@@ -3698,19 +3830,19 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="D117" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E117" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F117">
         <v>-1400</v>
@@ -3736,16 +3868,16 @@
         <v>6</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C118" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="D118" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="E118" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="F118">
         <v>-2000</v>
@@ -3765,16 +3897,16 @@
         <v>6</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C120" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="D120" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E120" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F120">
         <v>-9000</v>
@@ -3791,16 +3923,16 @@
         <v>6</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C122" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="D122" t="s">
         <v>18</v>
       </c>
       <c r="E122" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -3826,16 +3958,16 @@
         <v>6</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C123" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="D123" t="s">
         <v>20</v>
       </c>
       <c r="E123" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -3861,16 +3993,16 @@
         <v>6</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="C125" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="D125" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="E125" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="F125">
         <v>12000</v>
@@ -3887,11 +4019,11 @@
         <v>6</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>